--- a/Data_clean/MCAS/Estados_US/Edos_USA_2019/HAWAII_2019.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2019/HAWAII_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Total</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -599,7 +654,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Villa de Álvarez</t>
+          <t>Villa De Álvarez</t>
         </is>
       </c>
       <c r="C17">
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -625,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -654,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -680,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -693,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -706,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -732,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -745,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Total</t>
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Total</t>
@@ -791,7 +901,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -807,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C32">
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -846,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -859,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tepetlixpa</t>
@@ -872,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C37">
@@ -885,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -898,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -911,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -955,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>León</t>
@@ -968,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -981,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -1007,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1027,7 +1212,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C48">
@@ -1038,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C49">
@@ -1051,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C50">
@@ -1064,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1095,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Ajacuba</t>
@@ -1108,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C54">
@@ -1121,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1152,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Cabo Corrientes</t>
@@ -1165,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>El Salto</t>
@@ -1178,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1191,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -1204,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C61">
@@ -1217,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C62">
@@ -1230,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -1243,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -1256,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1269,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C66">
@@ -1282,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C67">
@@ -1295,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1308,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Yahualica de González Gallo</t>
+          <t>Yahualica De González Gallo</t>
         </is>
       </c>
       <c r="C69">
@@ -1321,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -1334,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C71">
@@ -1347,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1391,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1404,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -1417,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -1430,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Villamar</t>
@@ -1443,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1456,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1469,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1500,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -1513,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1544,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Rosamorada</t>
@@ -1557,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1570,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1583,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1592,7 +1957,7 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>0.09659090909090909</v>
+        <v>0.09659090909090907</v>
       </c>
     </row>
     <row r="90">
@@ -1603,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C90">
@@ -1614,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C91">
@@ -1627,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Constancia del Rosario</t>
+          <t>Constancia Del Rosario</t>
         </is>
       </c>
       <c r="C92">
@@ -1640,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fresnillo de Trujano</t>
+          <t>Fresnillo De Trujano</t>
         </is>
       </c>
       <c r="C93">
@@ -1653,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C94">
@@ -1666,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C95">
@@ -1679,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -1692,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>San Juan Teitipac</t>
@@ -1705,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -1718,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Santiago Comaltepec</t>
@@ -1731,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Santiago Tilantongo</t>
@@ -1744,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Santo Domingo Armenta</t>
@@ -1757,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Santo Tomás Ocotepec</t>
@@ -1770,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C103">
@@ -1783,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1814,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -1827,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -1840,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C108">
@@ -1853,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1866,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -1879,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C111">
@@ -1892,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Xayacatlán de Bravo</t>
+          <t>Xayacatlán De Bravo</t>
         </is>
       </c>
       <c r="C112">
@@ -1905,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1925,7 +2400,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C114">
@@ -1936,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1949,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1980,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -1993,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2024,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2055,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C123">
@@ -2068,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Ixtaczoquitlán</t>
@@ -2081,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -2094,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -2107,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2138,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2169,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -2182,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2205,41 +2745,6 @@
       </c>
       <c r="D133">
         <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
